--- a/backtest-ksj/results/backtest_summary.xlsx
+++ b/backtest-ksj/results/backtest_summary.xlsx
@@ -5025,7 +5025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>Point-in-Time 시가총액 상위 300 (KOSPI+KOSDAQ, 분기 시총 ffill, 생존편향 없음)</t>
+          <t>Point-in-Time 시가총액 상위 300 (KOSPI+KOSDAQ, 분기 시총 ffill; 현재 생존자 전용 리스트는 아님. 단, 원천 캐시 커버리지 한계 존재)</t>
         </is>
       </c>
     </row>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>KODEX 200 (벤치마크)</t>
+          <t>KODEX 200 (벤치마크), 가격수익률 기준(분배금·세금 미반영)</t>
         </is>
       </c>
     </row>
@@ -5316,6 +5316,18 @@
       <c r="B28" s="9" t="inlineStr">
         <is>
           <t>리밸런싱 시점 중 n_hold==0(무투자, 현금 100%)인 비율. 위험회피 발동 또는 종목선정 실패 시 발생.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>방법론 주의</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>유니버스는 현재 생존자 전용 리스트가 아니지만 상장폐지 전체 커버리지는 원천 data/cache 범위에 의존. KODEX200 벤치마크는 분배금 재투자 총수익률이 아닌 가격수익률 기준.</t>
         </is>
       </c>
     </row>

--- a/backtest-ksj/results/backtest_summary.xlsx
+++ b/backtest-ksj/results/backtest_summary.xlsx
@@ -33,6 +33,8 @@
     <sheet name="s1w-sp500" sheetId="24" state="visible" r:id="rId24"/>
     <sheet name="s2w-sp500" sheetId="25" state="visible" r:id="rId25"/>
     <sheet name="s3w-sp500" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="s1m_lsv" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="s1m_kang" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -533,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1935,117 +1937,117 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>069500(월간 환산)</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>벤치마크: KODEX200 매수후보유</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="n">
-        <v>24.72</v>
-      </c>
-      <c r="G29" s="7" t="n">
-        <v>-36.12</v>
-      </c>
-      <c r="H29" s="7" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="I29" s="7" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="J29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="7" t="n">
-        <v>0</v>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>s1m_lsv</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>KR섹터Fama-LSV</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>US섹터 SPDR 모멘텀 상위3섹터-&gt;한국 FnGuide섹터 매핑-&gt;섹터내 Fama-LSV(PER·PBR 저평가) 7/5/3 동일가중 | 위험회피 없음(항상 100% 투자)</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>20.63</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-24.9</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>708</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="5" t="n">
+        <v>8.109999999999999</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>069500(주간 환산)</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>벤치마크: KODEX200 매수후보유</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="n">
-        <v>24.72</v>
-      </c>
-      <c r="G30" s="7" t="n">
-        <v>-36.12</v>
-      </c>
-      <c r="H30" s="7" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="I30" s="7" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="J30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="7" t="n">
-        <v>0</v>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>s1m_kang</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>KR섹터Kang우량주</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>US섹터 모멘텀 상위3섹터-&gt;섹터내 Kang우량주(①시총하위50% ②영업현금흐름&gt;0&amp;순익&gt;0 ③영업이익/자산 높은순) 7/5/3 동일가중 | 위험회피 없음(항상 100% 투자)</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>31.27</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>-19.26</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>716</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>18.83</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="M30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>8.109999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>SP500(월간 환산)</t>
+          <t>069500(월간 환산)</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -2065,20 +2067,20 @@
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>벤치마크: S&amp;P500 매수후보유</t>
+          <t>벤치마크: KODEX200 매수후보유</t>
         </is>
       </c>
       <c r="F31" s="7" t="n">
-        <v>16.1</v>
+        <v>24.72</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>-33.92</v>
+        <v>-36.12</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>0.76</v>
+        <v>0.99</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>0.47</v>
+        <v>0.68</v>
       </c>
       <c r="J31" s="7" t="n">
         <v>0</v>
@@ -2099,54 +2101,162 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
+          <t>069500(주간 환산)</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>벤치마크: KODEX200 매수후보유</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>24.72</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>-36.12</v>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>SP500(월간 환산)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>벤치마크: S&amp;P500 매수후보유</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="G33" s="7" t="n">
+        <v>-33.92</v>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
           <t>SP500(주간 환산)</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>벤치마크: S&amp;P500 매수후보유</t>
         </is>
       </c>
-      <c r="F32" s="7" t="n">
+      <c r="F34" s="7" t="n">
         <v>16.1</v>
       </c>
-      <c r="G32" s="7" t="n">
+      <c r="G34" s="7" t="n">
         <v>-33.92</v>
       </c>
-      <c r="H32" s="7" t="n">
+      <c r="H34" s="7" t="n">
         <v>0.76</v>
       </c>
-      <c r="I32" s="7" t="n">
+      <c r="I34" s="7" t="n">
         <v>0.47</v>
       </c>
-      <c r="J32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="7" t="n">
+      <c r="J34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14907,6 +15017,1460 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>s1m_lsv — S1-월간 (US섹터Top3→KR Fama-LSV 7/5/3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>캐던스: 월간(월말 평가)   |   종목선정: US섹터 SPDR 모멘텀 상위3섹터-&gt;한국 FnGuide섹터 매핑-&gt;섹터내 Fama-LSV(PER·PBR 저평가) 7/5/3 동일가중   |   실행: 익월 첫 거래일 시초가 진입(한국 종목, 수정주가)   |   비교 벤치마크: KODEX200</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>위험회피: 위험회피 없음(항상 100% 투자)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>현금비중(OOS, 2019-01~2026-05):</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>현금비중(전체기간):</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>구간</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>세그먼트</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>기간</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>CAGR</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>MDD</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Sharpe</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Calmar</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>매매횟수</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>누적거래비용%</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>연환산비용%</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>현금비중%</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>벤치(KODEX200) CAGR</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>벤치(KODEX200) MDD</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>벤치(KODEX200) Sharpe</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>벤치(KODEX200) Calmar</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>CAGR 초과분(전략-벤치)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Fold1</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>IS(학습)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>2014-01-01 ~ 2018-12-31</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-29.13</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>451</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>-23.34</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="P8" s="14" t="n">
+        <v>-1.37</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Fold1</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>OOS(검증)</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>2019-01-01 ~ 2020-12-31</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>-24.9</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>204</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>22.71</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>-34.75</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="O9" s="5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="P9" s="14" t="n">
+        <v>-15.27</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Fold2</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>IS(학습)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>2016-01-01 ~ 2020-12-31</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-37.42</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>568</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>-40.65</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="P10" s="14" t="n">
+        <v>-8.68</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Fold2</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>OOS(검증)</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>2021-01-01 ~ 2022-12-31</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>22.04</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-15.65</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>194</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>-14.68</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>-36.12</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="O11" s="5" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="P11" s="15" t="n">
+        <v>36.72</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Fold3</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>IS(학습)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>2018-01-01 ~ 2022-12-31</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>-32.98</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>518</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>-2.11</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>-40.65</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P12" s="15" t="n">
+        <v>10.16</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Fold3</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>OOS(검증)</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>2023-01-01 ~ 2024-12-31</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-10.42</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>182</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>-21.14</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="O13" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="P13" s="14" t="n">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Fold4</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>IS(학습)</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>2020-01-01 ~ 2024-12-31</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-22.77</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>499</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>-36.12</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O14" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P14" s="15" t="n">
+        <v>13.19</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Fold4</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>OOS(검증)</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>2025-01-01 ~ 2026-05-31</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>71.56999999999999</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>-2.33</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>128</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>179.04</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>-20.62</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O15" s="5" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="P15" s="14" t="n">
+        <v>-107.47</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>ALL_OOS</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>OOS(검증)</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>2019-01-01 ~ 2026-05-31</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>20.63</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>-24.9</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>708</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="K16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="7" t="n">
+        <v>24.72</v>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>-36.12</v>
+      </c>
+      <c r="N16" s="7" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="O16" s="7" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="P16" s="16" t="n">
+        <v>-4.09</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>2015-01-01 ~ 2026-06-30</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>-37.42</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>1183</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>23.06</v>
+      </c>
+      <c r="J17" s="7" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="K17" s="7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L17" s="7" t="n">
+        <v>17.69</v>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>-40.65</v>
+      </c>
+      <c r="N17" s="7" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="O17" s="7" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="P17" s="16" t="n">
+        <v>-4.32</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="A2:N2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>s1m_kang — S1-월간 (US섹터Top3→KR Kang우량주 7/5/3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>캐던스: 월간(월말 평가)   |   종목선정: US섹터 모멘텀 상위3섹터-&gt;섹터내 Kang우량주(①시총하위50% ②영업현금흐름&gt;0&amp;순익&gt;0 ③영업이익/자산 높은순) 7/5/3 동일가중   |   실행: 익월 첫 거래일 시초가 진입(한국 종목, 수정주가)   |   비교 벤치마크: KODEX200</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>위험회피: 위험회피 없음(항상 100% 투자)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>현금비중(OOS, 2019-01~2026-05):</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>현금비중(전체기간):</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>구간</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>세그먼트</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>기간</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>CAGR</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>MDD</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Sharpe</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Calmar</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>매매횟수</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>누적거래비용%</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>연환산비용%</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>현금비중%</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>벤치(KODEX200) CAGR</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>벤치(KODEX200) MDD</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>벤치(KODEX200) Sharpe</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>벤치(KODEX200) Calmar</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>CAGR 초과분(전략-벤치)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Fold1</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>IS(학습)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>2014-01-01 ~ 2018-12-31</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-28.49</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>459</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>-23.34</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="P8" s="15" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Fold1</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>OOS(검증)</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>2019-01-01 ~ 2020-12-31</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>-19.26</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>203</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>22.71</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>-34.75</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="O9" s="5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="P9" s="14" t="n">
+        <v>-3.8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Fold2</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>IS(학습)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>2016-01-01 ~ 2020-12-31</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-33.35</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>565</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>-40.65</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="P10" s="14" t="n">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Fold2</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>OOS(검증)</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>2021-01-01 ~ 2022-12-31</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>35.55</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-11.88</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>199</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>-14.68</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>-36.12</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="O11" s="5" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="P11" s="15" t="n">
+        <v>50.23</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Fold3</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>IS(학습)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>2018-01-01 ~ 2022-12-31</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>15.07</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>-33.35</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>532</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>-2.11</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>-40.65</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P12" s="15" t="n">
+        <v>17.19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Fold3</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>OOS(검증)</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>2023-01-01 ~ 2024-12-31</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-14.81</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>187</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>-21.14</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="O13" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="P13" s="15" t="n">
+        <v>7.98</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Fold4</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>IS(학습)</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>2020-01-01 ~ 2024-12-31</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>26.86</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-19.26</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>485</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>-36.12</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O14" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P14" s="15" t="n">
+        <v>25.16</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Fold4</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>OOS(검증)</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>2025-01-01 ~ 2026-05-31</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>-5.82</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>127</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>179.04</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>-20.62</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O15" s="5" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="P15" s="14" t="n">
+        <v>-99.43000000000001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>ALL_OOS</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>OOS(검증)</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>2019-01-01 ~ 2026-05-31</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>31.27</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>-19.26</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>716</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>18.83</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="K16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="7" t="n">
+        <v>24.72</v>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>-36.12</v>
+      </c>
+      <c r="N16" s="7" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="O16" s="7" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="P16" s="18" t="n">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>2015-01-01 ~ 2026-06-30</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>-33.35</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>1185</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>28.38</v>
+      </c>
+      <c r="J17" s="7" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="K17" s="7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L17" s="7" t="n">
+        <v>17.69</v>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>-40.65</v>
+      </c>
+      <c r="N17" s="7" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="O17" s="7" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="P17" s="18" t="n">
+        <v>2.11</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="A2:N2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
